--- a/data_lake/bronze/LISTADO_DE_DESTINACIONES.xlsx
+++ b/data_lake/bronze/LISTADO_DE_DESTINACIONES.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Información\proyectos\aduana_bi\data_lake\bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0379816C-ED10-4AB9-8ADA-B47A26915848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7551F974-5F41-4051-9FD3-3F9AA72DC796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$78</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="164">
   <si>
     <t>CÓD.</t>
   </si>
@@ -331,12 +331,6 @@
     <t>DESPACHO SIMPLIFICADO PARA IMPORTACIONES MENORES</t>
   </si>
   <si>
-    <t>ER04</t>
-  </si>
-  <si>
-    <t>EXPORT A CONSUMO DE EXP. C/ RESERVA RETORNO C/ TRANF.</t>
-  </si>
-  <si>
     <t>NO APLICA LA DESTINACION AL REGIMEN</t>
   </si>
   <si>
@@ -344,12 +338,6 @@
   </si>
   <si>
     <t>IMPORTACIÓN A CONSUMO DE EXP. C/ RESERVA DE RETORNO</t>
-  </si>
-  <si>
-    <t>IR10</t>
-  </si>
-  <si>
-    <t>IMPORT A CONSUMO DE EXP. C/ RESERVA RETORNO C/ TRANF.</t>
   </si>
   <si>
     <t>ZF01</t>
@@ -654,7 +642,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -670,12 +658,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -976,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
@@ -996,7 +978,7 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1646,41 +1628,45 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="17"/>
+      <c r="C48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="6" t="s">
         <v>106</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="11.25" customHeight="1">
-      <c r="A50" s="7" t="s">
+    <row r="50" spans="1:4">
+      <c r="A50" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C50" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" s="17"/>
+      <c r="C50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="5" t="s">
@@ -1690,10 +1676,10 @@
         <v>110</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1704,7 +1690,7 @@
         <v>112</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>14</v>
@@ -1718,10 +1704,10 @@
         <v>114</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1774,7 +1760,7 @@
         <v>122</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>14</v>
@@ -1788,7 +1774,7 @@
         <v>124</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>14</v>
@@ -1805,7 +1791,7 @@
         <v>6</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1816,10 +1802,10 @@
         <v>128</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1833,7 +1819,7 @@
         <v>6</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1850,7 +1836,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" ht="11.25" customHeight="1">
       <c r="A63" s="5" t="s">
         <v>133</v>
       </c>
@@ -1875,10 +1861,10 @@
         <v>34</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="11.25" customHeight="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" s="5" t="s">
         <v>137</v>
       </c>
@@ -1889,7 +1875,7 @@
         <v>6</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1900,10 +1886,10 @@
         <v>140</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1917,34 +1903,34 @@
         <v>6</v>
       </c>
       <c r="D67" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="5" t="s">
+    <row r="69" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A69" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" s="4" t="s">
+      <c r="C69" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" s="11" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1955,91 +1941,91 @@
       <c r="B70" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="C70" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="12.75" customHeight="1">
-      <c r="A71" s="12" t="s">
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>14</v>
+      <c r="C71" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
+      <c r="C72" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D73" s="13" t="s">
+      <c r="D75" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C76" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>14</v>
+      <c r="C76" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2049,58 +2035,28 @@
       <c r="B77" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D77" s="15"/>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D77" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="C79" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D79" s="17"/>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>25</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C79:D79"/>
+  <mergeCells count="1">
+    <mergeCell ref="C77:D77"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.196850393700787" top="0" bottom="0.35433070866141703" header="0.31496062992126" footer="0.31496062992126"/>
